--- a/data/trans_orig/P1433-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2012</t>
+          <t>Población con diagnóstico de esterilidad en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7289</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7057</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>7560</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6967</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307397</t>
+          <t>307165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>744698</t>
+          <t>744105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414185</t>
+          <t>413760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333065</t>
+          <t>333025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>749559</t>
+          <t>750106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623740</t>
+          <t>622999</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255317</t>
+          <t>254450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>881968</t>
+          <t>881967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888649</t>
+          <t>889544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1760,82 +1760,82 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2053</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5235</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1044</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5222</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1156956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1159009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>759500</t>
+          <t>759487</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1918491</t>
+          <t>1918504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504249</t>
+          <t>504298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751778</t>
+          <t>751806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759352</t>
+          <t>759354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1258631</t>
+          <t>1259210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268824</t>
+          <t>1268840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2446,97 +2446,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6824</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2178</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7601</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6552</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2178</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>7678</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1099679</t>
+          <t>1100456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1366483</t>
+          <t>1367609</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>19807</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3411650</t>
+          <t>3411334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3420110</t>
+          <t>3420085</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3527255</t>
+          <t>3525036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3539861</t>
+          <t>3539600</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6942332</t>
+          <t>6942736</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6958240</t>
+          <t>6957870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2016</t>
+          <t>Población con diagnóstico de esterilidad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,97 +3366,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>347055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774103</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>776147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,62 +3744,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7467</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6566</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370839</t>
+          <t>369703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742934</t>
+          <t>742033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4052,97 +4052,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519922</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>686022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>688036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1145145</t>
+          <t>1145182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>821318</t>
+          <t>820731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1969501</t>
+          <t>1968860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4738,97 +4738,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>618713</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>620706</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>738244</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1356938</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1358950</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5081,97 +5081,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6135</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5129</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4703</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1076896</t>
+          <t>1075890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1364467</t>
+          <t>1364039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3378032</t>
+          <t>3377335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3384832</t>
+          <t>3384830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3524432</t>
+          <t>3525462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6906505</t>
+          <t>6906527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6915389</t>
+          <t>6916242</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1433-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Clase-trans_orig.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307165</t>
+          <t>308012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>744105</t>
+          <t>744771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413760</t>
+          <t>414359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333025</t>
+          <t>333864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>750106</t>
+          <t>749787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622999</t>
+          <t>622953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254450</t>
+          <t>256058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>881967</t>
+          <t>881144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>889544</t>
+          <t>888649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>759487</t>
+          <t>759486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1918504</t>
+          <t>1918206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504298</t>
+          <t>504506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751806</t>
+          <t>751520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759354</t>
+          <t>759351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1259210</t>
+          <t>1259125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268840</t>
+          <t>1268837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1100456</t>
+          <t>1098751</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1367609</t>
+          <t>1366554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3411334</t>
+          <t>3412124</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3420085</t>
+          <t>3420072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3525036</t>
+          <t>3525462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3539600</t>
+          <t>3539829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6942736</t>
+          <t>6942590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6957870</t>
+          <t>6958519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369703</t>
+          <t>369894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742033</t>
+          <t>742609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1145182</t>
+          <t>1144304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>820731</t>
+          <t>820521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1968860</t>
+          <t>1969003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1075890</t>
+          <t>1076917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1364039</t>
+          <t>1364069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3377335</t>
+          <t>3377981</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3384830</t>
+          <t>3384835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3525462</t>
+          <t>3525173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6906527</t>
+          <t>6906486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6916242</t>
+          <t>6915408</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,97%</t>
         </is>
       </c>
     </row>
